--- a/data/processed/positivacao/2023-04_positivacao_anonimizado.xlsx
+++ b/data/processed/positivacao/2023-04_positivacao_anonimizado.xlsx
@@ -551,7 +551,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Vendedor: 1 - ROBSON</t>
+          <t>Vendedor: 1 - VENDEDOR 01</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -26739,7 +26739,7 @@
     <row r="1016">
       <c r="A1016" t="inlineStr">
         <is>
-          <t>Vendedor: 3 - FERNANDA</t>
+          <t>Vendedor: 3 - VENDEDOR 03</t>
         </is>
       </c>
       <c r="B1016" t="inlineStr"/>
@@ -38195,7 +38195,7 @@
     <row r="1457">
       <c r="A1457" t="inlineStr">
         <is>
-          <t>Vendedor: 4 - DANIELA</t>
+          <t>Vendedor: 4 - VENDEDOR 04</t>
         </is>
       </c>
       <c r="B1457" t="inlineStr"/>
@@ -66463,7 +66463,7 @@
     <row r="2545">
       <c r="A2545" t="inlineStr">
         <is>
-          <t>Vendedor: 8 - RAFAEL</t>
+          <t>Vendedor: 8 - VENDEDOR 08</t>
         </is>
       </c>
       <c r="B2545" t="inlineStr"/>
@@ -68056,12 +68056,12 @@
       <c r="A2607" t="inlineStr"/>
       <c r="B2607" t="inlineStr">
         <is>
-          <t>Vendedor 1 - ROBSON: positivou 9 cliente(s), não positivou 87 cliente(s) - Total vendido: R$ 6.842,04
+          <t>Vendedor 1 - VENDEDOR 01: positivou 9 cliente(s), não positivou 87 cliente(s) - Total vendido: R$ 6.842,04
 Vendedor 18 - LOJA: positivou 210 cliente(s), não positivou 700 cliente(s) - Total vendido: R$ 127.675,83
-Vendedor 3 - FERNANDA: positivou 110 cliente(s), não positivou 330 cliente(s) - Total vendido: R$ 129.371,74
-Vendedor 4 - DANIELA: positivou 70 cliente(s), não positivou 582 cliente(s) - Total vendido: R$ 38.665,39
+Vendedor 3 - VENDEDOR 03: positivou 110 cliente(s), não positivou 330 cliente(s) - Total vendido: R$ 129.371,74
+Vendedor 4 - VENDEDOR 04: positivou 70 cliente(s), não positivou 582 cliente(s) - Total vendido: R$ 38.665,39
 Vendedor 5 - SITE: positivou 11 cliente(s), não positivou 423 cliente(s) - Total vendido: R$ 1.690,85
-Vendedor 8 - RAFAEL: positivou 0 cliente(s), não positivou 60 cliente(s) - Total vendido: R$ 0,00</t>
+Vendedor 8 - VENDEDOR 08: positivou 0 cliente(s), não positivou 60 cliente(s) - Total vendido: R$ 0,00</t>
         </is>
       </c>
       <c r="C2607" t="inlineStr"/>
